--- a/P3_DEP_LEBL.xlsx
+++ b/P3_DEP_LEBL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://enaire-my.sharepoint.com/personal/aprades_enaire_es/Documents/Docs/Mi Universidad/2018-PGTA/P3_new/250702/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmart\Desktop\Arnau Uni\PGTA-P3\PGTA-P3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="8_{9E958623-B562-4D3F-B6BF-D406326454CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCB12A5F-BB2D-4351-AD74-17D4742318CB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{148F37B6-5292-46C7-A3F6-F9430F60FE94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8FEBBB81-CF7C-4874-A147-0F0C77E01815}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8FEBBB81-CF7C-4874-A147-0F0C77E01815}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -3695,10 +3695,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4019,14 +4015,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F86D83EB-8A07-4465-B782-D9217F22D920}">
   <dimension ref="A1:L540"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="5" width="16.140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="121.42578125" customWidth="1"/>
+    <col min="5" max="5" width="16.109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="121.44140625" customWidth="1"/>
+    <col min="9" max="9" width="13.44140625" customWidth="1"/>
     <col min="11" max="11" width="18" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4064,7 +4061,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>537</v>
       </c>
@@ -4102,7 +4099,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>538</v>
       </c>
@@ -4140,7 +4137,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>539</v>
       </c>
@@ -4178,7 +4175,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>541</v>
       </c>
@@ -4216,7 +4213,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>542</v>
       </c>
@@ -4254,7 +4251,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>543</v>
       </c>
@@ -4292,7 +4289,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>544</v>
       </c>
@@ -4330,7 +4327,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>545</v>
       </c>
@@ -4368,7 +4365,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>546</v>
       </c>
@@ -4406,7 +4403,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>547</v>
       </c>
@@ -4444,7 +4441,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>548</v>
       </c>
@@ -4482,7 +4479,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>549</v>
       </c>
@@ -4520,7 +4517,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>550</v>
       </c>
@@ -4558,7 +4555,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>551</v>
       </c>
@@ -4596,7 +4593,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>552</v>
       </c>
@@ -4634,7 +4631,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>553</v>
       </c>
@@ -4672,7 +4669,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>554</v>
       </c>
@@ -4710,7 +4707,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>555</v>
       </c>
@@ -4748,7 +4745,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>556</v>
       </c>
@@ -4786,7 +4783,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>557</v>
       </c>
@@ -4824,7 +4821,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>558</v>
       </c>
@@ -4862,7 +4859,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>559</v>
       </c>
@@ -4900,7 +4897,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>560</v>
       </c>
@@ -4938,7 +4935,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>561</v>
       </c>
@@ -4976,7 +4973,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>562</v>
       </c>
@@ -5014,7 +5011,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>563</v>
       </c>
@@ -5052,7 +5049,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>564</v>
       </c>
@@ -5090,7 +5087,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>565</v>
       </c>
@@ -5128,7 +5125,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>566</v>
       </c>
@@ -5166,7 +5163,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>567</v>
       </c>
@@ -5204,7 +5201,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>568</v>
       </c>
@@ -5242,7 +5239,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>569</v>
       </c>
@@ -5280,7 +5277,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>570</v>
       </c>
@@ -5318,7 +5315,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>571</v>
       </c>
@@ -5356,7 +5353,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>572</v>
       </c>
@@ -5394,7 +5391,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>573</v>
       </c>
@@ -5432,7 +5429,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>575</v>
       </c>
@@ -5470,7 +5467,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>576</v>
       </c>
@@ -5508,7 +5505,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>577</v>
       </c>
@@ -5546,7 +5543,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>578</v>
       </c>
@@ -5584,7 +5581,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>579</v>
       </c>
@@ -5622,7 +5619,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>580</v>
       </c>
@@ -5660,7 +5657,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>581</v>
       </c>
@@ -5698,7 +5695,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>582</v>
       </c>
@@ -5736,7 +5733,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>583</v>
       </c>
@@ -5774,7 +5771,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>584</v>
       </c>
@@ -5812,7 +5809,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>585</v>
       </c>
@@ -5850,7 +5847,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>586</v>
       </c>
@@ -5888,7 +5885,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>587</v>
       </c>
@@ -5926,7 +5923,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>588</v>
       </c>
@@ -5964,7 +5961,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>589</v>
       </c>
@@ -6002,7 +5999,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>590</v>
       </c>
@@ -6040,7 +6037,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>591</v>
       </c>
@@ -6078,7 +6075,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>592</v>
       </c>
@@ -6116,7 +6113,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>593</v>
       </c>
@@ -6154,7 +6151,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>594</v>
       </c>
@@ -6192,7 +6189,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>595</v>
       </c>
@@ -6230,7 +6227,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>596</v>
       </c>
@@ -6268,7 +6265,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>597</v>
       </c>
@@ -6306,7 +6303,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>598</v>
       </c>
@@ -6344,7 +6341,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>599</v>
       </c>
@@ -6382,7 +6379,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>600</v>
       </c>
@@ -6420,7 +6417,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>601</v>
       </c>
@@ -6458,7 +6455,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>602</v>
       </c>
@@ -6496,7 +6493,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>603</v>
       </c>
@@ -6534,7 +6531,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>604</v>
       </c>
@@ -6572,7 +6569,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>605</v>
       </c>
@@ -6610,7 +6607,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>606</v>
       </c>
@@ -6648,7 +6645,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>607</v>
       </c>
@@ -6686,7 +6683,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>608</v>
       </c>
@@ -6724,7 +6721,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>609</v>
       </c>
@@ -6762,7 +6759,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>610</v>
       </c>
@@ -6800,7 +6797,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>611</v>
       </c>
@@ -6838,7 +6835,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>612</v>
       </c>
@@ -6876,7 +6873,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>613</v>
       </c>
@@ -6914,7 +6911,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>614</v>
       </c>
@@ -6952,7 +6949,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>615</v>
       </c>
@@ -6990,7 +6987,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>616</v>
       </c>
@@ -7028,7 +7025,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>617</v>
       </c>
@@ -7066,7 +7063,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>618</v>
       </c>
@@ -7104,7 +7101,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>619</v>
       </c>
@@ -7142,7 +7139,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>620</v>
       </c>
@@ -7180,7 +7177,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>621</v>
       </c>
@@ -7218,7 +7215,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>622</v>
       </c>
@@ -7256,7 +7253,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>623</v>
       </c>
@@ -7294,7 +7291,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>624</v>
       </c>
@@ -7332,7 +7329,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>625</v>
       </c>
@@ -7370,7 +7367,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>626</v>
       </c>
@@ -7408,7 +7405,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>627</v>
       </c>
@@ -7446,7 +7443,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>628</v>
       </c>
@@ -7484,7 +7481,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>629</v>
       </c>
@@ -7522,7 +7519,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>630</v>
       </c>
@@ -7560,7 +7557,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>631</v>
       </c>
@@ -7598,7 +7595,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>632</v>
       </c>
@@ -7636,7 +7633,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>633</v>
       </c>
@@ -7674,7 +7671,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>634</v>
       </c>
@@ -7712,7 +7709,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>635</v>
       </c>
@@ -7750,7 +7747,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>636</v>
       </c>
@@ -7788,7 +7785,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>637</v>
       </c>
@@ -7826,7 +7823,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>638</v>
       </c>
@@ -7864,7 +7861,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>639</v>
       </c>
@@ -7902,7 +7899,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>640</v>
       </c>
@@ -7940,7 +7937,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>641</v>
       </c>
@@ -7978,7 +7975,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>642</v>
       </c>
@@ -8016,7 +8013,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>643</v>
       </c>
@@ -8054,7 +8051,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>644</v>
       </c>
@@ -8092,7 +8089,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>645</v>
       </c>
@@ -8130,7 +8127,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>646</v>
       </c>
@@ -8168,7 +8165,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>647</v>
       </c>
@@ -8206,7 +8203,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>648</v>
       </c>
@@ -8244,7 +8241,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>649</v>
       </c>
@@ -8282,7 +8279,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>650</v>
       </c>
@@ -8320,7 +8317,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>651</v>
       </c>
@@ -8358,7 +8355,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>652</v>
       </c>
@@ -8396,7 +8393,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>653</v>
       </c>
@@ -8434,7 +8431,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>654</v>
       </c>
@@ -8472,7 +8469,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>655</v>
       </c>
@@ -8510,7 +8507,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>656</v>
       </c>
@@ -8548,7 +8545,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>657</v>
       </c>
@@ -8586,7 +8583,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>658</v>
       </c>
@@ -8624,7 +8621,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>659</v>
       </c>
@@ -8662,7 +8659,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>660</v>
       </c>
@@ -8700,7 +8697,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>661</v>
       </c>
@@ -8738,7 +8735,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>662</v>
       </c>
@@ -8776,7 +8773,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>663</v>
       </c>
@@ -8814,7 +8811,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>664</v>
       </c>
@@ -8852,7 +8849,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>665</v>
       </c>
@@ -8890,7 +8887,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>666</v>
       </c>
@@ -8928,7 +8925,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>667</v>
       </c>
@@ -8966,7 +8963,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>668</v>
       </c>
@@ -9004,7 +9001,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>669</v>
       </c>
@@ -9042,7 +9039,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>670</v>
       </c>
@@ -9080,7 +9077,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>671</v>
       </c>
@@ -9118,7 +9115,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>672</v>
       </c>
@@ -9156,7 +9153,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>673</v>
       </c>
@@ -9194,7 +9191,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>674</v>
       </c>
@@ -9232,7 +9229,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>675</v>
       </c>
@@ -9270,7 +9267,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>676</v>
       </c>
@@ -9308,7 +9305,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>677</v>
       </c>
@@ -9346,7 +9343,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>678</v>
       </c>
@@ -9384,7 +9381,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>679</v>
       </c>
@@ -9422,7 +9419,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>680</v>
       </c>
@@ -9460,7 +9457,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>681</v>
       </c>
@@ -9498,7 +9495,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>682</v>
       </c>
@@ -9536,7 +9533,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>683</v>
       </c>
@@ -9574,7 +9571,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>684</v>
       </c>
@@ -9612,7 +9609,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>685</v>
       </c>
@@ -9650,7 +9647,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>686</v>
       </c>
@@ -9688,7 +9685,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>687</v>
       </c>
@@ -9726,7 +9723,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>688</v>
       </c>
@@ -9764,7 +9761,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>689</v>
       </c>
@@ -9802,7 +9799,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>690</v>
       </c>
@@ -9840,7 +9837,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>691</v>
       </c>
@@ -9878,7 +9875,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>692</v>
       </c>
@@ -9916,7 +9913,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>693</v>
       </c>
@@ -9954,7 +9951,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>694</v>
       </c>
@@ -9992,7 +9989,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>695</v>
       </c>
@@ -10030,7 +10027,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>696</v>
       </c>
@@ -10068,7 +10065,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>697</v>
       </c>
@@ -10106,7 +10103,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>698</v>
       </c>
@@ -10144,7 +10141,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>699</v>
       </c>
@@ -10182,7 +10179,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>700</v>
       </c>
@@ -10220,7 +10217,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>701</v>
       </c>
@@ -10258,7 +10255,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>702</v>
       </c>
@@ -10296,7 +10293,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>703</v>
       </c>
@@ -10334,7 +10331,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>704</v>
       </c>
@@ -10372,7 +10369,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>705</v>
       </c>
@@ -10410,7 +10407,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>706</v>
       </c>
@@ -10448,7 +10445,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>707</v>
       </c>
@@ -10486,7 +10483,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>708</v>
       </c>
@@ -10524,7 +10521,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>709</v>
       </c>
@@ -10562,7 +10559,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>710</v>
       </c>
@@ -10600,7 +10597,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>711</v>
       </c>
@@ -10638,7 +10635,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>712</v>
       </c>
@@ -10676,7 +10673,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>713</v>
       </c>
@@ -10714,7 +10711,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>714</v>
       </c>
@@ -10752,7 +10749,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>715</v>
       </c>
@@ -10790,7 +10787,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>716</v>
       </c>
@@ -10828,7 +10825,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>718</v>
       </c>
@@ -10866,7 +10863,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>719</v>
       </c>
@@ -10904,7 +10901,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>720</v>
       </c>
@@ -10942,7 +10939,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>721</v>
       </c>
@@ -10980,7 +10977,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>722</v>
       </c>
@@ -11018,7 +11015,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>723</v>
       </c>
@@ -11056,7 +11053,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>724</v>
       </c>
@@ -11094,7 +11091,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>725</v>
       </c>
@@ -11132,7 +11129,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>726</v>
       </c>
@@ -11170,7 +11167,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>727</v>
       </c>
@@ -11208,7 +11205,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>728</v>
       </c>
@@ -11246,7 +11243,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>729</v>
       </c>
@@ -11284,7 +11281,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>730</v>
       </c>
@@ -11322,7 +11319,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>731</v>
       </c>
@@ -11360,7 +11357,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>732</v>
       </c>
@@ -11398,7 +11395,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>733</v>
       </c>
@@ -11436,7 +11433,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>734</v>
       </c>
@@ -11474,7 +11471,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>735</v>
       </c>
@@ -11512,7 +11509,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>736</v>
       </c>
@@ -11550,7 +11547,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>737</v>
       </c>
@@ -11588,7 +11585,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>738</v>
       </c>
@@ -11626,7 +11623,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>739</v>
       </c>
@@ -11664,7 +11661,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>740</v>
       </c>
@@ -11702,7 +11699,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>741</v>
       </c>
@@ -11740,7 +11737,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>742</v>
       </c>
@@ -11778,7 +11775,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>743</v>
       </c>
@@ -11816,7 +11813,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>744</v>
       </c>
@@ -11854,7 +11851,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>745</v>
       </c>
@@ -11892,7 +11889,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>746</v>
       </c>
@@ -11930,7 +11927,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>747</v>
       </c>
@@ -11968,7 +11965,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>748</v>
       </c>
@@ -12006,7 +12003,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>749</v>
       </c>
@@ -12044,7 +12041,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>750</v>
       </c>
@@ -12082,7 +12079,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>751</v>
       </c>
@@ -12120,7 +12117,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>752</v>
       </c>
@@ -12158,7 +12155,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>753</v>
       </c>
@@ -12196,7 +12193,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>754</v>
       </c>
@@ -12234,7 +12231,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>755</v>
       </c>
@@ -12272,7 +12269,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>756</v>
       </c>
@@ -12310,7 +12307,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>757</v>
       </c>
@@ -12348,7 +12345,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>758</v>
       </c>
@@ -12386,7 +12383,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>759</v>
       </c>
@@ -12424,7 +12421,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>760</v>
       </c>
@@ -12462,7 +12459,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>761</v>
       </c>
@@ -12500,7 +12497,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>762</v>
       </c>
@@ -12538,7 +12535,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>763</v>
       </c>
@@ -12576,7 +12573,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>764</v>
       </c>
@@ -12614,7 +12611,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>765</v>
       </c>
@@ -12652,7 +12649,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>766</v>
       </c>
@@ -12690,7 +12687,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>767</v>
       </c>
@@ -12728,7 +12725,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>768</v>
       </c>
@@ -12766,7 +12763,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>769</v>
       </c>
@@ -12804,7 +12801,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>770</v>
       </c>
@@ -12842,7 +12839,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>771</v>
       </c>
@@ -12880,7 +12877,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>772</v>
       </c>
@@ -12918,7 +12915,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>773</v>
       </c>
@@ -12956,7 +12953,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>774</v>
       </c>
@@ -12994,7 +12991,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>775</v>
       </c>
@@ -13032,7 +13029,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>776</v>
       </c>
@@ -13070,7 +13067,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>777</v>
       </c>
@@ -13108,7 +13105,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>778</v>
       </c>
@@ -13146,7 +13143,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="241" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>779</v>
       </c>
@@ -13184,7 +13181,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="242" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>780</v>
       </c>
@@ -13222,7 +13219,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="243" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>781</v>
       </c>
@@ -13260,7 +13257,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="244" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>782</v>
       </c>
@@ -13298,7 +13295,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="245" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>783</v>
       </c>
@@ -13336,7 +13333,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="246" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>784</v>
       </c>
@@ -13374,7 +13371,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="247" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>785</v>
       </c>
@@ -13412,7 +13409,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="248" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>786</v>
       </c>
@@ -13450,7 +13447,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="249" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>787</v>
       </c>
@@ -13488,7 +13485,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="250" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>788</v>
       </c>
@@ -13526,7 +13523,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="251" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>789</v>
       </c>
@@ -13564,7 +13561,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="252" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>790</v>
       </c>
@@ -13602,7 +13599,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="253" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>791</v>
       </c>
@@ -13640,7 +13637,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="254" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>792</v>
       </c>
@@ -13678,7 +13675,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="255" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>793</v>
       </c>
@@ -13716,7 +13713,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="256" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>794</v>
       </c>
@@ -13754,7 +13751,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="257" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>795</v>
       </c>
@@ -13792,7 +13789,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="258" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>796</v>
       </c>
@@ -13830,7 +13827,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="259" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>797</v>
       </c>
@@ -13868,7 +13865,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="260" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>798</v>
       </c>
@@ -13906,7 +13903,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="261" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>799</v>
       </c>
@@ -13944,7 +13941,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="262" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>800</v>
       </c>
@@ -13982,7 +13979,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="263" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>801</v>
       </c>
@@ -14020,7 +14017,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="264" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>802</v>
       </c>
@@ -14058,7 +14055,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="265" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>803</v>
       </c>
@@ -14096,7 +14093,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="266" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>804</v>
       </c>
@@ -14134,7 +14131,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="267" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>805</v>
       </c>
@@ -14172,7 +14169,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="268" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>806</v>
       </c>
@@ -14210,7 +14207,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="269" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>807</v>
       </c>
@@ -14248,7 +14245,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="270" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>808</v>
       </c>
@@ -14286,7 +14283,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="271" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>809</v>
       </c>
@@ -14324,7 +14321,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="272" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>810</v>
       </c>
@@ -14362,7 +14359,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="273" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>811</v>
       </c>
@@ -14400,7 +14397,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="274" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>812</v>
       </c>
@@ -14438,7 +14435,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="275" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>813</v>
       </c>
@@ -14476,7 +14473,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="276" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>814</v>
       </c>
@@ -14514,7 +14511,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="277" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>815</v>
       </c>
@@ -14552,7 +14549,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="278" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>816</v>
       </c>
@@ -14590,7 +14587,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="279" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>817</v>
       </c>
@@ -14628,7 +14625,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="280" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>818</v>
       </c>
@@ -14666,7 +14663,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="281" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>819</v>
       </c>
@@ -14704,7 +14701,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="282" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>820</v>
       </c>
@@ -14742,7 +14739,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="283" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>821</v>
       </c>
@@ -14780,7 +14777,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="284" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>822</v>
       </c>
@@ -14818,7 +14815,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="285" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>823</v>
       </c>
@@ -14856,7 +14853,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="286" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>824</v>
       </c>
@@ -14894,7 +14891,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="287" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>825</v>
       </c>
@@ -14932,7 +14929,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="288" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>826</v>
       </c>
@@ -14970,7 +14967,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="289" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>827</v>
       </c>
@@ -15008,7 +15005,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="290" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>828</v>
       </c>
@@ -15046,7 +15043,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="291" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>829</v>
       </c>
@@ -15084,7 +15081,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="292" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>830</v>
       </c>
@@ -15122,7 +15119,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="293" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>831</v>
       </c>
@@ -15160,7 +15157,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="294" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>832</v>
       </c>
@@ -15198,7 +15195,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="295" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>833</v>
       </c>
@@ -15236,7 +15233,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="296" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>834</v>
       </c>
@@ -15274,7 +15271,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="297" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>835</v>
       </c>
@@ -15312,7 +15309,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="298" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>836</v>
       </c>
@@ -15350,7 +15347,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="299" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>837</v>
       </c>
@@ -15388,7 +15385,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="300" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>838</v>
       </c>
@@ -15426,7 +15423,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="301" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>839</v>
       </c>
@@ -15464,7 +15461,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="302" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A302">
         <v>840</v>
       </c>
@@ -15502,7 +15499,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="303" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>841</v>
       </c>
@@ -15540,7 +15537,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="304" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>842</v>
       </c>
@@ -15578,7 +15575,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="305" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A305">
         <v>843</v>
       </c>
@@ -15616,7 +15613,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="306" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A306">
         <v>844</v>
       </c>
@@ -15654,7 +15651,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="307" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A307">
         <v>845</v>
       </c>
@@ -15692,7 +15689,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="308" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A308">
         <v>846</v>
       </c>
@@ -15730,7 +15727,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="309" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A309">
         <v>847</v>
       </c>
@@ -15768,7 +15765,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="310" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A310">
         <v>848</v>
       </c>
@@ -15806,7 +15803,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="311" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A311">
         <v>849</v>
       </c>
@@ -15844,7 +15841,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="312" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>850</v>
       </c>
@@ -15882,7 +15879,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="313" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>851</v>
       </c>
@@ -15920,7 +15917,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="314" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A314">
         <v>852</v>
       </c>
@@ -15958,7 +15955,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="315" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>853</v>
       </c>
@@ -15996,7 +15993,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="316" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A316">
         <v>854</v>
       </c>
@@ -16034,7 +16031,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="317" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>855</v>
       </c>
@@ -16072,7 +16069,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="318" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A318">
         <v>856</v>
       </c>
@@ -16110,7 +16107,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="319" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A319">
         <v>857</v>
       </c>
@@ -16148,7 +16145,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="320" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A320">
         <v>858</v>
       </c>
@@ -16186,7 +16183,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="321" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A321">
         <v>859</v>
       </c>
@@ -16224,7 +16221,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="322" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A322">
         <v>860</v>
       </c>
@@ -16262,7 +16259,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="323" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>861</v>
       </c>
@@ -16300,7 +16297,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="324" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A324">
         <v>862</v>
       </c>
@@ -16338,7 +16335,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="325" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A325">
         <v>863</v>
       </c>
@@ -16376,7 +16373,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="326" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A326">
         <v>864</v>
       </c>
@@ -16414,7 +16411,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="327" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A327">
         <v>865</v>
       </c>
@@ -16452,7 +16449,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="328" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A328">
         <v>866</v>
       </c>
@@ -16490,7 +16487,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="329" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A329">
         <v>867</v>
       </c>
@@ -16528,7 +16525,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="330" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A330">
         <v>868</v>
       </c>
@@ -16566,7 +16563,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="331" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A331">
         <v>869</v>
       </c>
@@ -16604,7 +16601,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="332" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A332">
         <v>870</v>
       </c>
@@ -16642,7 +16639,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="333" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A333">
         <v>871</v>
       </c>
@@ -16680,7 +16677,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="334" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A334">
         <v>872</v>
       </c>
@@ -16718,7 +16715,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="335" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A335">
         <v>873</v>
       </c>
@@ -16756,7 +16753,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="336" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A336">
         <v>874</v>
       </c>
@@ -16794,7 +16791,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="337" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A337">
         <v>875</v>
       </c>
@@ -16832,7 +16829,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="338" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A338">
         <v>876</v>
       </c>
@@ -16870,7 +16867,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="339" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A339">
         <v>877</v>
       </c>
@@ -16908,7 +16905,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="340" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A340">
         <v>878</v>
       </c>
@@ -16946,7 +16943,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="341" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A341">
         <v>879</v>
       </c>
@@ -16984,7 +16981,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="342" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A342">
         <v>880</v>
       </c>
@@ -17022,7 +17019,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="343" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A343">
         <v>881</v>
       </c>
@@ -17060,7 +17057,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="344" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A344">
         <v>882</v>
       </c>
@@ -17098,7 +17095,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="345" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A345">
         <v>883</v>
       </c>
@@ -17136,7 +17133,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="346" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A346">
         <v>884</v>
       </c>
@@ -17174,7 +17171,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="347" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A347">
         <v>885</v>
       </c>
@@ -17212,7 +17209,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="348" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A348">
         <v>886</v>
       </c>
@@ -17250,7 +17247,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="349" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A349">
         <v>887</v>
       </c>
@@ -17288,7 +17285,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="350" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A350">
         <v>888</v>
       </c>
@@ -17326,7 +17323,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="351" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A351">
         <v>889</v>
       </c>
@@ -17364,7 +17361,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="352" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A352">
         <v>890</v>
       </c>
@@ -17402,7 +17399,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="353" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A353">
         <v>891</v>
       </c>
@@ -17440,7 +17437,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="354" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A354">
         <v>892</v>
       </c>
@@ -17478,7 +17475,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="355" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A355">
         <v>893</v>
       </c>
@@ -17516,7 +17513,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="356" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A356">
         <v>894</v>
       </c>
@@ -17554,7 +17551,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="357" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A357">
         <v>895</v>
       </c>
@@ -17592,7 +17589,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="358" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A358">
         <v>896</v>
       </c>
@@ -17630,7 +17627,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="359" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A359">
         <v>897</v>
       </c>
@@ -17668,7 +17665,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="360" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A360">
         <v>898</v>
       </c>
@@ -17706,7 +17703,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="361" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A361">
         <v>899</v>
       </c>
@@ -17744,7 +17741,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="362" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A362">
         <v>900</v>
       </c>
@@ -17782,7 +17779,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="363" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A363">
         <v>901</v>
       </c>
@@ -17820,7 +17817,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="364" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A364">
         <v>902</v>
       </c>
@@ -17858,7 +17855,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="365" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A365">
         <v>903</v>
       </c>
@@ -17896,7 +17893,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="366" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A366">
         <v>904</v>
       </c>
@@ -17934,7 +17931,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="367" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A367">
         <v>905</v>
       </c>
@@ -17972,7 +17969,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="368" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A368">
         <v>906</v>
       </c>
@@ -18010,7 +18007,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="369" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A369">
         <v>907</v>
       </c>
@@ -18048,7 +18045,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="370" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A370">
         <v>908</v>
       </c>
@@ -18086,7 +18083,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="371" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A371">
         <v>909</v>
       </c>
@@ -18124,7 +18121,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="372" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A372">
         <v>910</v>
       </c>
@@ -18162,7 +18159,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="373" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A373">
         <v>911</v>
       </c>
@@ -18200,7 +18197,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="374" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A374">
         <v>912</v>
       </c>
@@ -18238,7 +18235,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="375" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A375">
         <v>913</v>
       </c>
@@ -18276,7 +18273,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="376" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A376">
         <v>914</v>
       </c>
@@ -18314,7 +18311,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="377" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A377">
         <v>915</v>
       </c>
@@ -18352,7 +18349,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="378" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A378">
         <v>916</v>
       </c>
@@ -18390,7 +18387,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="379" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A379">
         <v>917</v>
       </c>
@@ -18428,7 +18425,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="380" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A380">
         <v>918</v>
       </c>
@@ -18466,7 +18463,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="381" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A381">
         <v>919</v>
       </c>
@@ -18504,7 +18501,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="382" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A382">
         <v>920</v>
       </c>
@@ -18542,7 +18539,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="383" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A383">
         <v>921</v>
       </c>
@@ -18580,7 +18577,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="384" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A384">
         <v>922</v>
       </c>
@@ -18618,7 +18615,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="385" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A385">
         <v>923</v>
       </c>
@@ -18656,7 +18653,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="386" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A386">
         <v>924</v>
       </c>
@@ -18694,7 +18691,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="387" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A387">
         <v>925</v>
       </c>
@@ -18732,7 +18729,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="388" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A388">
         <v>926</v>
       </c>
@@ -18770,7 +18767,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="389" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A389">
         <v>927</v>
       </c>
@@ -18808,7 +18805,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="390" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A390">
         <v>928</v>
       </c>
@@ -18846,7 +18843,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="391" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A391">
         <v>929</v>
       </c>
@@ -18884,7 +18881,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="392" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A392">
         <v>930</v>
       </c>
@@ -18922,7 +18919,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="393" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A393">
         <v>931</v>
       </c>
@@ -18960,7 +18957,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="394" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A394">
         <v>932</v>
       </c>
@@ -18998,7 +18995,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="395" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A395">
         <v>933</v>
       </c>
@@ -19036,7 +19033,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="396" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A396">
         <v>934</v>
       </c>
@@ -19074,7 +19071,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="397" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A397">
         <v>935</v>
       </c>
@@ -19112,7 +19109,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="398" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A398">
         <v>936</v>
       </c>
@@ -19150,7 +19147,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="399" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A399">
         <v>937</v>
       </c>
@@ -19188,7 +19185,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="400" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A400">
         <v>938</v>
       </c>
@@ -19226,7 +19223,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="401" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A401">
         <v>939</v>
       </c>
@@ -19264,7 +19261,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="402" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A402">
         <v>940</v>
       </c>
@@ -19302,7 +19299,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="403" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A403">
         <v>941</v>
       </c>
@@ -19340,7 +19337,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="404" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A404">
         <v>942</v>
       </c>
@@ -19378,7 +19375,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="405" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A405">
         <v>943</v>
       </c>
@@ -19416,7 +19413,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="406" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A406">
         <v>944</v>
       </c>
@@ -19454,7 +19451,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="407" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A407">
         <v>945</v>
       </c>
@@ -19492,7 +19489,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="408" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A408">
         <v>946</v>
       </c>
@@ -19530,7 +19527,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="409" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A409">
         <v>947</v>
       </c>
@@ -19568,7 +19565,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="410" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A410">
         <v>948</v>
       </c>
@@ -19606,7 +19603,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="411" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A411">
         <v>949</v>
       </c>
@@ -19644,7 +19641,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="412" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A412">
         <v>950</v>
       </c>
@@ -19682,7 +19679,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="413" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A413">
         <v>951</v>
       </c>
@@ -19720,7 +19717,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="414" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A414">
         <v>952</v>
       </c>
@@ -19758,7 +19755,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="415" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A415">
         <v>953</v>
       </c>
@@ -19796,7 +19793,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="416" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A416">
         <v>954</v>
       </c>
@@ -19834,7 +19831,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="417" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A417">
         <v>955</v>
       </c>
@@ -19872,7 +19869,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="418" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A418">
         <v>956</v>
       </c>
@@ -19910,7 +19907,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="419" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A419">
         <v>957</v>
       </c>
@@ -19948,7 +19945,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="420" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A420">
         <v>958</v>
       </c>
@@ -19986,7 +19983,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="421" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A421">
         <v>959</v>
       </c>
@@ -20024,7 +20021,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="422" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A422">
         <v>960</v>
       </c>
@@ -20062,7 +20059,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="423" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A423">
         <v>961</v>
       </c>
@@ -20100,7 +20097,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="424" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A424">
         <v>962</v>
       </c>
@@ -20138,7 +20135,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="425" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A425">
         <v>963</v>
       </c>
@@ -20176,7 +20173,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="426" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A426">
         <v>964</v>
       </c>
@@ -20214,7 +20211,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="427" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A427">
         <v>965</v>
       </c>
@@ -20252,7 +20249,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="428" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A428">
         <v>966</v>
       </c>
@@ -20290,7 +20287,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="429" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A429">
         <v>967</v>
       </c>
@@ -20328,7 +20325,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="430" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A430">
         <v>968</v>
       </c>
@@ -20366,7 +20363,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="431" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A431">
         <v>969</v>
       </c>
@@ -20404,7 +20401,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="432" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A432">
         <v>970</v>
       </c>
@@ -20442,7 +20439,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="433" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A433">
         <v>971</v>
       </c>
@@ -20480,7 +20477,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="434" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A434">
         <v>972</v>
       </c>
@@ -20518,7 +20515,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="435" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A435">
         <v>973</v>
       </c>
@@ -20556,7 +20553,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="436" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A436">
         <v>974</v>
       </c>
@@ -20594,7 +20591,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="437" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A437">
         <v>975</v>
       </c>
@@ -20632,7 +20629,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="438" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A438">
         <v>976</v>
       </c>
@@ -20670,7 +20667,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="439" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A439">
         <v>977</v>
       </c>
@@ -20708,7 +20705,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="440" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A440">
         <v>978</v>
       </c>
@@ -20746,7 +20743,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="441" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A441">
         <v>979</v>
       </c>
@@ -20784,7 +20781,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="442" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A442">
         <v>980</v>
       </c>
@@ -20822,7 +20819,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="443" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A443">
         <v>981</v>
       </c>
@@ -20860,7 +20857,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="444" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A444">
         <v>982</v>
       </c>
@@ -20898,7 +20895,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="445" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A445">
         <v>983</v>
       </c>
@@ -20936,7 +20933,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="446" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A446">
         <v>984</v>
       </c>
@@ -20974,7 +20971,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="447" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A447">
         <v>985</v>
       </c>
@@ -21012,7 +21009,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="448" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A448">
         <v>986</v>
       </c>
@@ -21050,7 +21047,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="449" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A449">
         <v>987</v>
       </c>
@@ -21088,7 +21085,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="450" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A450">
         <v>988</v>
       </c>
@@ -21126,7 +21123,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="451" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A451">
         <v>989</v>
       </c>
@@ -21164,7 +21161,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="452" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A452">
         <v>990</v>
       </c>
@@ -21202,7 +21199,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="453" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A453">
         <v>991</v>
       </c>
@@ -21240,7 +21237,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="454" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A454">
         <v>992</v>
       </c>
@@ -21278,7 +21275,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="455" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A455">
         <v>993</v>
       </c>
@@ -21316,7 +21313,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="456" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A456">
         <v>994</v>
       </c>
@@ -21354,7 +21351,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="457" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A457">
         <v>995</v>
       </c>
@@ -21392,7 +21389,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="458" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A458">
         <v>996</v>
       </c>
@@ -21430,7 +21427,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="459" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A459">
         <v>997</v>
       </c>
@@ -21468,7 +21465,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="460" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A460">
         <v>998</v>
       </c>
@@ -21506,7 +21503,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="461" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A461">
         <v>999</v>
       </c>
@@ -21544,7 +21541,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="462" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A462">
         <v>1000</v>
       </c>
@@ -21582,7 +21579,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="463" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A463">
         <v>1001</v>
       </c>
@@ -21620,7 +21617,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="464" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A464">
         <v>1002</v>
       </c>
@@ -21658,7 +21655,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="465" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A465">
         <v>1003</v>
       </c>
@@ -21696,7 +21693,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="466" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A466">
         <v>1004</v>
       </c>
@@ -21734,7 +21731,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="467" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A467">
         <v>1005</v>
       </c>
@@ -21772,7 +21769,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="468" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A468">
         <v>1006</v>
       </c>
@@ -21810,7 +21807,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="469" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A469">
         <v>1007</v>
       </c>
@@ -21848,7 +21845,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="470" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A470">
         <v>1008</v>
       </c>
@@ -21886,7 +21883,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="471" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A471">
         <v>1009</v>
       </c>
@@ -21924,7 +21921,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="472" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A472">
         <v>1010</v>
       </c>
@@ -21962,7 +21959,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="473" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A473">
         <v>1011</v>
       </c>
@@ -22000,7 +21997,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="474" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A474">
         <v>1012</v>
       </c>
@@ -22038,7 +22035,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="475" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A475">
         <v>1013</v>
       </c>
@@ -22076,7 +22073,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="476" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A476">
         <v>1014</v>
       </c>
@@ -22114,7 +22111,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="477" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A477">
         <v>1015</v>
       </c>
@@ -22152,7 +22149,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="478" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A478">
         <v>1016</v>
       </c>
@@ -22190,7 +22187,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="479" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A479">
         <v>1017</v>
       </c>
@@ -22228,7 +22225,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="480" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A480">
         <v>1018</v>
       </c>
@@ -22266,7 +22263,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="481" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A481">
         <v>1019</v>
       </c>
@@ -22304,7 +22301,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="482" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A482">
         <v>1020</v>
       </c>
@@ -22342,7 +22339,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="483" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A483">
         <v>1021</v>
       </c>
@@ -22380,7 +22377,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="484" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A484">
         <v>1022</v>
       </c>
@@ -22418,7 +22415,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="485" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A485">
         <v>1023</v>
       </c>
@@ -22456,7 +22453,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="486" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A486">
         <v>1024</v>
       </c>
@@ -22494,7 +22491,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="487" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A487">
         <v>1025</v>
       </c>
@@ -22532,7 +22529,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="488" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A488">
         <v>1026</v>
       </c>
@@ -22570,7 +22567,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="489" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A489">
         <v>1027</v>
       </c>
@@ -22608,7 +22605,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="490" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A490">
         <v>1028</v>
       </c>
@@ -22646,7 +22643,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="491" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A491">
         <v>1029</v>
       </c>
@@ -22684,7 +22681,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="492" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A492">
         <v>1030</v>
       </c>
@@ -22722,7 +22719,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="493" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A493">
         <v>1031</v>
       </c>
@@ -22760,7 +22757,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="494" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A494">
         <v>1032</v>
       </c>
@@ -22798,7 +22795,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="495" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A495">
         <v>1033</v>
       </c>
@@ -22836,7 +22833,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="496" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A496">
         <v>1034</v>
       </c>
@@ -22874,7 +22871,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="497" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A497">
         <v>1035</v>
       </c>
@@ -22912,7 +22909,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="498" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A498">
         <v>1036</v>
       </c>
@@ -22950,7 +22947,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="499" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A499">
         <v>1037</v>
       </c>
@@ -22988,7 +22985,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="500" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A500">
         <v>1038</v>
       </c>
@@ -23026,7 +23023,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="501" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A501">
         <v>1039</v>
       </c>
@@ -23064,7 +23061,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="502" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A502">
         <v>1040</v>
       </c>
@@ -23102,7 +23099,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="503" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A503">
         <v>1041</v>
       </c>
@@ -23140,7 +23137,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="504" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A504">
         <v>1042</v>
       </c>
@@ -23178,7 +23175,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="505" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A505">
         <v>1043</v>
       </c>
@@ -23216,7 +23213,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="506" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A506">
         <v>1044</v>
       </c>
@@ -23254,7 +23251,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="507" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A507">
         <v>1045</v>
       </c>
@@ -23292,7 +23289,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="508" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A508">
         <v>1046</v>
       </c>
@@ -23330,7 +23327,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="509" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A509">
         <v>1047</v>
       </c>
@@ -23368,7 +23365,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="510" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A510">
         <v>1048</v>
       </c>
@@ -23406,7 +23403,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="511" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A511">
         <v>1049</v>
       </c>
@@ -23444,7 +23441,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="512" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A512">
         <v>1050</v>
       </c>
@@ -23482,7 +23479,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="513" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A513">
         <v>1051</v>
       </c>
@@ -23520,7 +23517,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="514" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A514">
         <v>1052</v>
       </c>
@@ -23558,7 +23555,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="515" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A515">
         <v>1053</v>
       </c>
@@ -23596,7 +23593,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="516" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A516">
         <v>1054</v>
       </c>
@@ -23634,7 +23631,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="517" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A517">
         <v>1055</v>
       </c>
@@ -23672,7 +23669,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="518" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A518">
         <v>1056</v>
       </c>
@@ -23710,7 +23707,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="519" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A519">
         <v>1057</v>
       </c>
@@ -23748,7 +23745,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="520" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A520">
         <v>1058</v>
       </c>
@@ -23786,7 +23783,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="521" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A521">
         <v>1059</v>
       </c>
@@ -23824,7 +23821,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="522" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A522">
         <v>1060</v>
       </c>
@@ -23862,7 +23859,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="523" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A523">
         <v>1061</v>
       </c>
@@ -23900,7 +23897,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="524" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A524">
         <v>1062</v>
       </c>
@@ -23938,7 +23935,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="525" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A525">
         <v>1063</v>
       </c>
@@ -23976,7 +23973,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="526" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A526">
         <v>1064</v>
       </c>
@@ -24014,7 +24011,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="527" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A527">
         <v>1065</v>
       </c>
@@ -24052,7 +24049,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="528" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A528">
         <v>1066</v>
       </c>
@@ -24090,7 +24087,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="529" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A529">
         <v>1067</v>
       </c>
@@ -24128,7 +24125,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="530" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A530">
         <v>1068</v>
       </c>
@@ -24166,7 +24163,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="531" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A531">
         <v>1069</v>
       </c>
@@ -24204,7 +24201,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="532" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A532">
         <v>1070</v>
       </c>
@@ -24242,7 +24239,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="533" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A533">
         <v>1071</v>
       </c>
@@ -24280,7 +24277,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="534" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A534">
         <v>1072</v>
       </c>
@@ -24318,7 +24315,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="535" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A535">
         <v>1073</v>
       </c>
@@ -24356,7 +24353,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="536" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A536">
         <v>1074</v>
       </c>
@@ -24394,7 +24391,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="537" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A537">
         <v>1075</v>
       </c>
@@ -24432,7 +24429,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="538" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A538">
         <v>1076</v>
       </c>
@@ -24470,7 +24467,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="539" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A539">
         <v>1077</v>
       </c>
@@ -24508,7 +24505,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="540" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A540">
         <v>1078</v>
       </c>
